--- a/data/trending_integrated_20261006_13.xlsx
+++ b/data/trending_integrated_20261006_13.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52675426640</v>
+        <v>52726829150</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -619,23 +619,23 @@
         <v>6000</v>
       </c>
       <c r="R2" t="n">
-        <v>574000</v>
+        <v>553000</v>
       </c>
       <c r="S2" t="n">
         <v>-34000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 FDA 승인 관련 기대감. 기타법인 자사주 매집 및 유증 물량 소화.</t>
+          <t>HLB제약의 유상증자 물량 소화 및 기타법인 자사주 매집 확인. 리보세라닙 미국 승인 신청 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유증', '신약', '자사주']</t>
+          <t>['유상증자', '자사주 매집', '리보세라닙']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17760</v>
+        <v>46900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.62%</t>
+          <t>'+15.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>695</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>404</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>4284</v>
       </c>
       <c r="H3" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K3" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L3" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M3" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N3" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>98191803555</v>
+        <v>238384104800</v>
       </c>
       <c r="P3" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>41000</v>
+        <v>425000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>HLB, FDA 실사 결과 기반 신약 승인 기대감 고조. 매도 이유 없는 강한 상승세 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA 실사', '신약 승인', '간암 치료제']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46700</v>
+        <v>17680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.45%</t>
+          <t>'+15.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>671</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>397</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>4187</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K4" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L4" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M4" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N4" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>234868403775</v>
+        <v>99268259560</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R4" t="n">
-        <v>477000</v>
+        <v>-37000</v>
       </c>
       <c r="S4" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB, FDA 실사 결과 기반 신약 승인 기대감 고조. 매도 이유 없는 강한 상승세 전망.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA 실사', '신약 승인', '간암 치료제']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4930</v>
+        <v>4945</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.05%</t>
+          <t>'+12.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
         <v>155</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>128224103488</v>
+        <v>129020621141</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -895,10 +895,10 @@
         <v>592</v>
       </c>
       <c r="R5" t="n">
-        <v>2718000</v>
+        <v>2597000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3090</v>
+        <v>20400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.61%</t>
+          <t>'+8.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2845</v>
+        <v>18790</v>
       </c>
       <c r="K6" t="n">
-        <v>3200</v>
+        <v>21400</v>
       </c>
       <c r="L6" t="n">
-        <v>3360</v>
+        <v>22300</v>
       </c>
       <c r="M6" t="n">
-        <v>2995</v>
+        <v>20050</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>45183853562</v>
+        <v>134917164890</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-8000</v>
+        <v>-73000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>은행 보안 강화 수혜 기대감. 금융 고객사 다수 보유 및 양자 보안 성장 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['보안주', '양자보안', '금융고객사']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20350</v>
+        <v>3080</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.30%</t>
+          <t>'+8.26%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K7" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M7" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>134015408440</v>
+        <v>45713763517</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-64000</v>
+        <v>35000</v>
       </c>
       <c r="S7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>은행 보안 강화 수혜 기대감. 금융 고객사 다수 보유 및 양자 보안 성장 가능성.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '금융고객사']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.54%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H8" t="n">
         <v>1.09</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>19558278759</v>
+        <v>19586638216</v>
       </c>
       <c r="P8" t="n">
         <v>2970</v>
@@ -1171,7 +1171,7 @@
         <v>890</v>
       </c>
       <c r="R8" t="n">
-        <v>-15000</v>
+        <v>-186000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18330</v>
+        <v>18350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+3.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>200076801555</v>
+        <v>202017811650</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1263,10 +1263,10 @@
         <v>1272</v>
       </c>
       <c r="R9" t="n">
-        <v>679000</v>
+        <v>656000</v>
       </c>
       <c r="S9" t="n">
-        <v>-4000</v>
+        <v>-9000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17730</v>
+        <v>17720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>49331717695</v>
+        <v>50608664220</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,10 +1355,10 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>381000</v>
+        <v>531000</v>
       </c>
       <c r="S10" t="n">
-        <v>-45000</v>
+        <v>-136000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15400</v>
+        <v>15190</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="H11" t="n">
         <v>0.32</v>
@@ -1438,7 +1438,7 @@
         <v>0.18</v>
       </c>
       <c r="O11" t="n">
-        <v>64529402525</v>
+        <v>65906122740</v>
       </c>
       <c r="P11" t="n">
         <v>29750</v>
@@ -1447,14 +1447,14 @@
         <v>12760</v>
       </c>
       <c r="R11" t="n">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지, 기타법인 자사주 매집 확인. 주가 상승 기대감 있으나 불확실성 존재.</t>
+          <t>기타법인 자사주 매집에 대한 기대감과 함께 초저평가 분석. 하지만 회사 측 무대응과 패턴 반복으로 인한 보수적 관점.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 매입', '초저평가', '신규 상장']</t>
+          <t>['자사주 매집', '초저평가', '무대응']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19620</v>
+        <v>19640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
         <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.73</v>
       </c>
       <c r="O12" t="n">
-        <v>33220316620</v>
+        <v>33876057085</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1539,23 +1539,23 @@
         <v>18440</v>
       </c>
       <c r="R12" t="n">
-        <v>-412000</v>
+        <v>-603000</v>
       </c>
       <c r="S12" t="n">
-        <v>-26000</v>
+        <v>-43000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성중공업, 수주 기대감과 함께 주가 부진에 대한 불만 표출. 브랜드 가치 활용 요구.</t>
+          <t>조선주 전반의 하락세 속에서 삼성중공업의 부진에 대한 부정적 시각. 대규모 수주 기대에도 주가 부진 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '주가 부진', '브랜드 가치']</t>
+          <t>['조선주', '수주', '주가 부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>270750</v>
+        <v>271500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G13" t="n">
-        <v>1546</v>
+        <v>1523</v>
       </c>
       <c r="H13" t="n">
         <v>46.41</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>2038610048500</v>
+        <v>2090428820000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1631,23 +1631,23 @@
         <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-779000</v>
+        <v>-1259000</v>
       </c>
       <c r="S13" t="n">
-        <v>311000</v>
+        <v>374000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자, 60만원대 기대감 속 자사주 매입 비판과 실적 하락 우려 제기. 정치적 이슈 언급.</t>
+          <t>자사주 매입 중단 및 수급 붕괴에 대한 비판적 전망. 부정적 실적 기대와 정치적 논란.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '실적 하락', '수급 붕괴']</t>
+          <t>['자사주 매입', '수급 붕괴', '영업이익']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1783000</v>
+        <v>1781000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-3.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G14" t="n">
-        <v>1934</v>
+        <v>1873</v>
       </c>
       <c r="H14" t="n">
         <v>49.76</v>
@@ -1708,13 +1708,13 @@
         <v>1837000</v>
       </c>
       <c r="M14" t="n">
-        <v>1782000</v>
+        <v>1781000</v>
       </c>
       <c r="N14" t="n">
         <v>49.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2703300714500</v>
+        <v>2777266939500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1723,23 +1723,23 @@
         <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>-331000</v>
+        <v>-549000</v>
       </c>
       <c r="S14" t="n">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스, 오너 리스크 및 국장 악재로 인한 주가 하락세. ADR 상장 후 외국인 수급 우려.</t>
+          <t>오너 리스크 및 정치적 요인에 따른 SK하이닉스 주가 하락에 대한 비판. 외국인 수급 우려와 부정적 주가 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너 리스크', '국장 악재', '외국인 수급']</t>
+          <t>['오너 리스크', '외국인 수급', '주가 전망']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261006_13.xlsx
+++ b/data/trending_integrated_20261006_13.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52726829150</v>
+        <v>52744509740</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB제약의 유상증자 물량 소화 및 기타법인 자사주 매집 확인. 리보세라닙 미국 승인 신청 관련 긍정적 전망.</t>
+          <t>리보세라닙 미국 승인 신청 및 유증 물량 소화 후 주가 상승 기대. 기타 법인 자사주 매집.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유상증자', '자사주 매집', '리보세라닙']</t>
+          <t>['리보세라닙', '유증', '자사주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46900</v>
+        <v>47150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.95%</t>
+          <t>'+16.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="F3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G3" t="n">
-        <v>4284</v>
+        <v>4377</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>238384104800</v>
+        <v>240304424375</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17680</v>
+        <v>17750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.10%</t>
+          <t>'+15.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
         <v>2.17</v>
@@ -794,7 +794,7 @@
         <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>99268259560</v>
+        <v>99706336465</v>
       </c>
       <c r="P4" t="n">
         <v>38400</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4945</v>
+        <v>4990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.39%</t>
+          <t>'+13.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>129020621141</v>
+        <v>130460306059</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20400</v>
+        <v>3110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.57%</t>
+          <t>'+9.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K6" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L6" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M6" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>134917164890</v>
+        <v>45997978274</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>-73000</v>
+        <v>35000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>은행 보안 강화 수혜 기대감. 금융 고객사 다수 보유 및 양자 보안 성장 가능성.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '금융고객사']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,82 +1011,82 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3080</v>
+        <v>1454</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.26%</t>
+          <t>'+8.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>-0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2845</v>
+        <v>1340</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>1370</v>
       </c>
       <c r="L7" t="n">
-        <v>3360</v>
+        <v>1555</v>
       </c>
       <c r="M7" t="n">
-        <v>2995</v>
+        <v>1360</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>45713763517</v>
+        <v>19687781064</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>2970</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>890</v>
       </c>
       <c r="R7" t="n">
-        <v>35000</v>
+        <v>-186000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,99 +1108,99 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1443</v>
+        <v>20350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+8.30%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K8" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L8" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M8" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>19586638216</v>
+        <v>135535868590</v>
       </c>
       <c r="P8" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q8" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>-186000</v>
+        <v>-73000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>은행 보안 강화 수혜 기대감. 금융 고객사 다수 보유 및 양자 보안 성장 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '양자보안', '금융고객사']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18350</v>
+        <v>18370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>202017811650</v>
+        <v>203173995095</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 증시 호조 및 3분기 영업이익 증가 기반 상승세 전망. 전고점 돌파 기대.</t>
+          <t>미국 증시 강세 및 3분기 영업이익 개선에 따른 상승 기대. 외인 순매수세 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '전고점']</t>
+          <t>['광통신', '영업이익', '외인 순매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17720</v>
+        <v>17700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+0.51%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>50608664220</v>
+        <v>51570967330</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15190</v>
+        <v>15330</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.04%</t>
+          <t>'-0.13%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.14</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
         <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H11" t="n">
         <v>0.32</v>
@@ -1438,7 +1438,7 @@
         <v>0.18</v>
       </c>
       <c r="O11" t="n">
-        <v>65906122740</v>
+        <v>66434343325</v>
       </c>
       <c r="P11" t="n">
         <v>29750</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집에 대한 기대감과 함께 초저평가 분석. 하지만 회사 측 무대응과 패턴 반복으로 인한 보수적 관점.</t>
+          <t>거래량 미미 및 주가 변동성 부재. 회사 대응 부재 및 자본잠식 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 매집', '초저평가', '무대응']</t>
+          <t>['초저평가', '주포', '자본잠식']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19640</v>
+        <v>19630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.60%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.73</v>
       </c>
       <c r="O12" t="n">
-        <v>33876057085</v>
+        <v>34365373520</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락세 속에서 삼성중공업의 부진에 대한 부정적 시각. 대규모 수주 기대에도 주가 부진 지속.</t>
+          <t>수주 기대에도 불구하고 주가 부진 지속. 업종 평균 대비 낮은 수익률에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '수주', '주가 부진']</t>
+          <t>['수주', '조선주', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>271500</v>
+        <v>271000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="G13" t="n">
-        <v>1523</v>
+        <v>1516</v>
       </c>
       <c r="H13" t="n">
         <v>46.41</v>
@@ -1622,7 +1622,7 @@
         <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>2090428820000</v>
+        <v>2127867915500</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 매입 중단 및 수급 붕괴에 대한 비판적 전망. 부정적 실적 기대와 정치적 논란.</t>
+          <t>자사주 매입 중단 및 실적 악화 전망. 정치적 이슈와 엮인 부정적 여론.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '수급 붕괴', '영업이익']</t>
+          <t>['자사주 매입', '영업이익', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1781000</v>
+        <v>1781500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.26%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="G14" t="n">
-        <v>1873</v>
+        <v>1911</v>
       </c>
       <c r="H14" t="n">
         <v>49.76</v>
@@ -1708,13 +1708,13 @@
         <v>1837000</v>
       </c>
       <c r="M14" t="n">
-        <v>1781000</v>
+        <v>1780000</v>
       </c>
       <c r="N14" t="n">
         <v>49.77</v>
       </c>
       <c r="O14" t="n">
-        <v>2777266939500</v>
+        <v>2878506366500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>오너 리스크 및 정치적 요인에 따른 SK하이닉스 주가 하락에 대한 비판. 외국인 수급 우려와 부정적 주가 전망.</t>
+          <t>오너 리스크 및 정치적 요인으로 인한 주가 하락 우려. 외국인 매도세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너 리스크', '외국인 수급', '주가 전망']</t>
+          <t>['오너리스크', '정치적 리스크', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261006_13.xlsx
+++ b/data/trending_integrated_20261006_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52744509740</v>
+        <v>52753213430</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>리보세라닙 미국 승인 신청 및 유증 물량 소화 후 주가 상승 기대. 기타 법인 자사주 매집.</t>
+          <t>HLB 간암 신약 리보세라닙의 미국 승인 신청 및 VAI(Validation of AI) 호재. 유증 물량 소화 및 기타 법인의 자사주 매집 확인. 2연상 가능성 및 N자형 파동 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['리보세라닙', '유증', '자사주']</t>
+          <t>['리보세라닙', 'VAI', '유증']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47150</v>
+        <v>6920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.56%</t>
+          <t>'+25.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>710</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>405</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>4377</v>
+        <v>112</v>
       </c>
       <c r="H3" t="n">
-        <v>14.1</v>
+        <v>1.87</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40450</v>
+        <v>5500</v>
       </c>
       <c r="K3" t="n">
-        <v>42700</v>
+        <v>6170</v>
       </c>
       <c r="L3" t="n">
-        <v>50700</v>
+        <v>6930</v>
       </c>
       <c r="M3" t="n">
-        <v>42150</v>
+        <v>5920</v>
       </c>
       <c r="N3" t="n">
-        <v>14.11</v>
+        <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>240304424375</v>
+        <v>80932837135</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R3" t="n">
-        <v>425000</v>
+        <v>60000</v>
       </c>
       <c r="S3" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB, FDA 실사 결과 기반 신약 승인 기대감 고조. 매도 이유 없는 강한 상승세 전망.</t>
+          <t>우리은행 해킹 방어 관련 티오리, 진트웹 공동 세일즈 파트너십 언급. 3분기 흑자 및 보안주 신고가 흐름 속 시총 낮은 점 고려. 재료 발생 시 매수 기회.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 실사', '신약 승인', '간암 치료제']</t>
+          <t>['보안주', '흑자', '시총']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17750</v>
+        <v>46850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.56%</t>
+          <t>'+15.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>727</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>408</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
+        <v>4433</v>
       </c>
       <c r="H4" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L4" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M4" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>99706336465</v>
+        <v>241303686500</v>
       </c>
       <c r="P4" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>-37000</v>
+        <v>425000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>리보세라닙의 FDA 실사 결과 및 완제의약품 제조시설 확인, 간암 신약 승인 기대감 고조. AI 기반 분석 및 동진셀온과의 연관성 언급. 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['리보세라닙', 'FDA', '간암 신약']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4990</v>
+        <v>17750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.41%</t>
+          <t>'+15.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4400</v>
+        <v>15360</v>
       </c>
       <c r="K5" t="n">
-        <v>4435</v>
+        <v>18000</v>
       </c>
       <c r="L5" t="n">
-        <v>5130</v>
+        <v>18640</v>
       </c>
       <c r="M5" t="n">
-        <v>4305</v>
+        <v>16800</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>130460306059</v>
+        <v>100135332300</v>
       </c>
       <c r="P5" t="n">
-        <v>8100</v>
+        <v>38400</v>
       </c>
       <c r="Q5" t="n">
-        <v>592</v>
+        <v>8010</v>
       </c>
       <c r="R5" t="n">
-        <v>2597000</v>
+        <v>-37000</v>
       </c>
       <c r="S5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인매수', '상한가', '반도체']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3110</v>
+        <v>5010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.31%</t>
+          <t>'+13.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2845</v>
+        <v>4400</v>
       </c>
       <c r="K6" t="n">
-        <v>3200</v>
+        <v>4435</v>
       </c>
       <c r="L6" t="n">
-        <v>3360</v>
+        <v>5130</v>
       </c>
       <c r="M6" t="n">
-        <v>2995</v>
+        <v>4305</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>45997978274</v>
+        <v>133453723952</v>
       </c>
       <c r="P6" t="n">
-        <v>4810</v>
+        <v>8100</v>
       </c>
       <c r="Q6" t="n">
-        <v>1400</v>
+        <v>592</v>
       </c>
       <c r="R6" t="n">
-        <v>35000</v>
+        <v>2597000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>해외 반도체 기업 급등에 따른 연동 기대감. 외국인 매수세 집중 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['외국인매수', '상한가', '반도체']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1454</v>
+        <v>3105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.51%</t>
+          <t>'+9.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1340</v>
+        <v>2845</v>
       </c>
       <c r="K7" t="n">
-        <v>1370</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>1555</v>
+        <v>3360</v>
       </c>
       <c r="M7" t="n">
-        <v>1360</v>
+        <v>2995</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>19687781064</v>
+        <v>46520075461</v>
       </c>
       <c r="P7" t="n">
-        <v>2970</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>890</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-186000</v>
+        <v>35000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>135535868590</v>
+        <v>136050444465</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1207,171 +1207,171 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18370</v>
+        <v>1449</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+8.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>743</v>
+        <v>192</v>
       </c>
       <c r="H9" t="n">
-        <v>3.81</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17800</v>
+        <v>1340</v>
       </c>
       <c r="K9" t="n">
-        <v>18040</v>
+        <v>1370</v>
       </c>
       <c r="L9" t="n">
-        <v>18880</v>
+        <v>1555</v>
       </c>
       <c r="M9" t="n">
-        <v>17950</v>
+        <v>1360</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>203173995095</v>
+        <v>19747890607</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>2970</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>890</v>
       </c>
       <c r="R9" t="n">
-        <v>656000</v>
+        <v>-186000</v>
       </c>
       <c r="S9" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 강세 및 3분기 영업이익 개선에 따른 상승 기대. 외인 순매수세 유입.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '외인 순매수']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17700</v>
+        <v>18410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.51%</t>
+          <t>'+3.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>464</v>
+        <v>774</v>
       </c>
       <c r="H10" t="n">
-        <v>9.390000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17610</v>
+        <v>17800</v>
       </c>
       <c r="K10" t="n">
-        <v>17700</v>
+        <v>18040</v>
       </c>
       <c r="L10" t="n">
-        <v>18160</v>
+        <v>18880</v>
       </c>
       <c r="M10" t="n">
-        <v>17630</v>
+        <v>17950</v>
       </c>
       <c r="N10" t="n">
-        <v>9.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>51570967330</v>
+        <v>205162475310</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>531000</v>
+        <v>656000</v>
       </c>
       <c r="S10" t="n">
-        <v>-136000</v>
+        <v>-9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
+          <t>미국 증시 광통신 섹터 강세 및 3분기 영업이익 증가, 루멘텀, 어플라이드옵토 등 연관 기업 상승. 현재 매물 소화 후 전고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주택 공급', '원전 테마', '허매도']</t>
+          <t>['광통신', '영업이익', '매물 소화']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,82 +1379,82 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15330</v>
+        <v>17740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.13%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>329</v>
+        <v>467</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15350</v>
+        <v>17610</v>
       </c>
       <c r="K11" t="n">
-        <v>14920</v>
+        <v>17700</v>
       </c>
       <c r="L11" t="n">
-        <v>16590</v>
+        <v>18160</v>
       </c>
       <c r="M11" t="n">
-        <v>14300</v>
+        <v>17630</v>
       </c>
       <c r="N11" t="n">
-        <v>0.18</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>66434343325</v>
+        <v>52659537090</v>
       </c>
       <c r="P11" t="n">
-        <v>29750</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>12760</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>13000</v>
+        <v>531000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-136000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 미미 및 주가 변동성 부재. 회사 대응 부재 및 자본잠식 우려.</t>
+          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,103 +1463,103 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['초저평가', '주포', '자본잠식']</t>
+          <t>['주택 공급', '원전 테마', '허매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19630</v>
+        <v>15230</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-0.78%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="H12" t="n">
-        <v>27.78</v>
+        <v>0.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19960</v>
+        <v>15350</v>
       </c>
       <c r="K12" t="n">
-        <v>20150</v>
+        <v>14920</v>
       </c>
       <c r="L12" t="n">
-        <v>20150</v>
+        <v>16590</v>
       </c>
       <c r="M12" t="n">
-        <v>19600</v>
+        <v>14300</v>
       </c>
       <c r="N12" t="n">
-        <v>27.73</v>
+        <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>34365373520</v>
+        <v>67229089860</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>29750</v>
       </c>
       <c r="Q12" t="n">
-        <v>18440</v>
+        <v>12760</v>
       </c>
       <c r="R12" t="n">
-        <v>-603000</v>
+        <v>13000</v>
       </c>
       <c r="S12" t="n">
-        <v>-43000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>수주 기대에도 불구하고 주가 부진 지속. 업종 평균 대비 낮은 수익률에 대한 불만.</t>
+          <t>거래량 미미 및 주가 변동성 부재. 회사 대응 부재 및 자본잠식 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '조선주', '주가']</t>
+          <t>['초저평가', '주포', '자본잠식']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>271000</v>
+        <v>19650</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-1.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>431</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>1516</v>
+        <v>296</v>
       </c>
       <c r="H13" t="n">
-        <v>46.41</v>
+        <v>27.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>276000</v>
+        <v>19960</v>
       </c>
       <c r="K13" t="n">
-        <v>278500</v>
+        <v>20150</v>
       </c>
       <c r="L13" t="n">
-        <v>279000</v>
+        <v>20150</v>
       </c>
       <c r="M13" t="n">
-        <v>270500</v>
+        <v>19600</v>
       </c>
       <c r="N13" t="n">
-        <v>46.41</v>
+        <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2127867915500</v>
+        <v>34794894865</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>18440</v>
       </c>
       <c r="R13" t="n">
-        <v>-1259000</v>
+        <v>-603000</v>
       </c>
       <c r="S13" t="n">
-        <v>374000</v>
+        <v>-43000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 매입 중단 및 실적 악화 전망. 정치적 이슈와 엮인 부정적 여론.</t>
+          <t>수주 기대에도 불구하고 주가 부진 지속. 업종 평균 대비 낮은 수익률에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '영업이익', '수급']</t>
+          <t>['수주', '조선주', '주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1781500</v>
+        <v>271000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>479</v>
+        <v>430</v>
       </c>
       <c r="G14" t="n">
-        <v>1911</v>
+        <v>1520</v>
       </c>
       <c r="H14" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K14" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L14" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M14" t="n">
-        <v>1780000</v>
+        <v>270500</v>
       </c>
       <c r="N14" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>2878506366500</v>
+        <v>2176429871500</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>-549000</v>
+        <v>-1259000</v>
       </c>
       <c r="S14" t="n">
-        <v>13000</v>
+        <v>374000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>오너 리스크 및 정치적 요인으로 인한 주가 하락 우려. 외국인 매도세.</t>
+          <t>분기 영업이익 100조 이상 예상에도 불구하고 주가 하락 우려, 자사주 매입 중단 및 ETF 상폐 관련 언급. 국내 증시 전반에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너리스크', '정치적 리스크', '외국인']</t>
+          <t>['영업이익', '자사주 매입', 'ETF']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1751,6 +1751,98 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1784000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-3.10%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E15" t="n">
+        <v>800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>471</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H15" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2944237930000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-549000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>오너 리스크(최태원 SK 주식 매각) 및 정치적 리스크(이재명, 윤석열 정부 관련 언급)로 인한 주가 하락 우려. ADR 상장 후 본주 외국인 수급 감소 지적.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['오너 리스크', '정치적 리스크', '외국인 수급']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_13.xlsx
+++ b/data/trending_integrated_20261006_13.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52753213430</v>
+        <v>52793076070</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 리보세라닙의 미국 승인 신청 및 VAI(Validation of AI) 호재. 유증 물량 소화 및 기타 법인의 자사주 매집 확인. 2연상 가능성 및 N자형 파동 분석.</t>
+          <t>HLB와의 연관성 및 유증 물량 소화 완료에 따른 주가 상승 기대감. FDA 승인 모멘텀 주목.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'VAI', '유증']</t>
+          <t>['HLB', '유증', 'FDA']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6920</v>
+        <v>7040</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+25.82%</t>
+          <t>'+28.00%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
         <v>112</v>
@@ -693,7 +693,7 @@
         <v>6170</v>
       </c>
       <c r="L3" t="n">
-        <v>6930</v>
+        <v>7050</v>
       </c>
       <c r="M3" t="n">
         <v>5920</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>80932837135</v>
+        <v>87352969725</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우리은행 해킹 방어 관련 티오리, 진트웹 공동 세일즈 파트너십 언급. 3분기 흑자 및 보안주 신고가 흐름 속 시총 낮은 점 고려. 재료 발생 시 매수 기회.</t>
+          <t>높은 수익률에 대한 기대감과 함께 상한가 가능성 언급. 보안주로서의 잠재력 주목.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '흑자', '시총']</t>
+          <t>['보안주', '상한가', '수익률']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46850</v>
+        <v>17740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.82%</t>
+          <t>'+15.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>727</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>408</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>4433</v>
+        <v>87</v>
       </c>
       <c r="H4" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K4" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L4" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M4" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N4" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>241303686500</v>
+        <v>100472862480</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R4" t="n">
-        <v>425000</v>
+        <v>-37000</v>
       </c>
       <c r="S4" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>리보세라닙의 FDA 실사 결과 및 완제의약품 제조시설 확인, 간암 신약 승인 기대감 고조. AI 기반 분석 및 동진셀온과의 연관성 언급. 주가 상승 전망.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA', '간암 신약']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17750</v>
+        <v>46650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.56%</t>
+          <t>'+15.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>736</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>412</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
+        <v>4506</v>
       </c>
       <c r="H5" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K5" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L5" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M5" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N5" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O5" t="n">
-        <v>100135332300</v>
+        <v>242850992100</v>
       </c>
       <c r="P5" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-37000</v>
+        <v>425000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>FDA 실사 결과 VAI 획득으로 신약 승인 기대감 최고조. 매도 이유 없다는 의견 지배적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA', '신약', 'VAI']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,12 +919,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.86%</t>
+          <t>'+14.09%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>133453723952</v>
+        <v>134612271202</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3105</v>
+        <v>3110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.14%</t>
+          <t>'+9.31%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>46520075461</v>
+        <v>46773883341</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20350</v>
+        <v>1457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.30%</t>
+          <t>'+8.73%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18790</v>
+        <v>1340</v>
       </c>
       <c r="K8" t="n">
-        <v>21400</v>
+        <v>1370</v>
       </c>
       <c r="L8" t="n">
-        <v>22300</v>
+        <v>1555</v>
       </c>
       <c r="M8" t="n">
-        <v>20050</v>
+        <v>1360</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>136050444465</v>
+        <v>19825018027</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>2970</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>890</v>
       </c>
       <c r="R8" t="n">
-        <v>-73000</v>
+        <v>-186000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>은행 보안 강화 수혜 기대감. 금융 고객사 다수 보유 및 양자 보안 성장 가능성.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '금융고객사']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1449</v>
+        <v>20400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.13%</t>
+          <t>'+8.57%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K9" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L9" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M9" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O9" t="n">
-        <v>19747890607</v>
+        <v>136376862140</v>
       </c>
       <c r="P9" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-186000</v>
+        <v>-73000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>은행권 보안 위협에 따른 보안주 상승 기대감. 엑스게이트의 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '양자보안', '금융권']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="n">
-        <v>774</v>
+        <v>793</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>205162475310</v>
+        <v>207185894730</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 3분기 영업이익 증가, 루멘텀, 어플라이드옵토 등 연관 기업 상승. 현재 매물 소화 후 전고점 돌파 기대.</t>
+          <t>광통신 섹터의 강세와 함께 대한광통신이 대장주로 부상할 것이라는 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매물 소화']</t>
+          <t>['광통신', '대장주', '매물 소화']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17740</v>
+        <v>17680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>52659537090</v>
+        <v>54168460980</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15230</v>
+        <v>15400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.78%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.14</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>67229089860</v>
+        <v>67828512010</v>
       </c>
       <c r="P12" t="n">
         <v>29750</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 미미 및 주가 변동성 부재. 회사 대응 부재 및 자본잠식 우려.</t>
+          <t>기타법인의 자사주 매집 사실은 있으나, 주가 움직임에 대한 불확실성과 회의적인 시각 공존.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['초저평가', '주포', '자본잠식']</t>
+          <t>['자사주', '프로그램', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19650</v>
+        <v>19630</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.55%</t>
+          <t>'-1.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H13" t="n">
         <v>27.78</v>
@@ -1622,7 +1622,7 @@
         <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>34794894865</v>
+        <v>35334298345</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>수주 기대에도 불구하고 주가 부진 지속. 업종 평균 대비 낮은 수익률에 대한 불만.</t>
+          <t>수주 기대감에도 불구하고 주가 부진에 대한 답답함과 불신 드러남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>271000</v>
+        <v>270250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-2.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G14" t="n">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="H14" t="n">
         <v>46.41</v>
@@ -1708,13 +1708,13 @@
         <v>279000</v>
       </c>
       <c r="M14" t="n">
-        <v>270500</v>
+        <v>270000</v>
       </c>
       <c r="N14" t="n">
         <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>2176429871500</v>
+        <v>2257738350250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>분기 영업이익 100조 이상 예상에도 불구하고 주가 하락 우려, 자사주 매입 중단 및 ETF 상폐 관련 언급. 국내 증시 전반에 대한 부정적 시각.</t>
+          <t>부정적인 의견 다수, 자사주 매입 중단 및 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주 매입', 'ETF']</t>
+          <t>['영업이익', '자사주', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1784000</v>
+        <v>1777000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.10%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G15" t="n">
-        <v>1872</v>
+        <v>1947</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1800,13 +1800,13 @@
         <v>1837000</v>
       </c>
       <c r="M15" t="n">
-        <v>1780000</v>
+        <v>1776000</v>
       </c>
       <c r="N15" t="n">
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>2944237930000</v>
+        <v>3059718780000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>오너 리스크(최태원 SK 주식 매각) 및 정치적 리스크(이재명, 윤석열 정부 관련 언급)로 인한 주가 하락 우려. ADR 상장 후 본주 외국인 수급 감소 지적.</t>
+          <t>정치적 리스크 및 오너 리스크로 인한 주가 하락에 대한 강한 불만 표출. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['오너 리스크', '정치적 리스크', '외국인 수급']</t>
+          <t>['오너리스크', '정치', '주가조작']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261006_13.xlsx
+++ b/data/trending_integrated_20261006_13.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52793076070</v>
+        <v>52822257500</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -670,7 +670,7 @@
         <v>0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
         <v>59</v>
@@ -693,7 +693,7 @@
         <v>6170</v>
       </c>
       <c r="L3" t="n">
-        <v>7050</v>
+        <v>7110</v>
       </c>
       <c r="M3" t="n">
         <v>5920</v>
@@ -702,7 +702,7 @@
         <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>87352969725</v>
+        <v>93318791420</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>높은 수익률에 대한 기대감과 함께 상한가 가능성 언급. 보안주로서의 잠재력 주목.</t>
+          <t>우리은행 해킹 방어 관련 티오리 협력 언급. 3분기 흑자 전환 및 보안주 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '상한가', '수익률']</t>
+          <t>['보안주', '양자암호', '흑자']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17740</v>
+        <v>17820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.49%</t>
+          <t>'+16.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>87</v>
@@ -794,7 +794,7 @@
         <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>100472862480</v>
+        <v>101485339880</v>
       </c>
       <c r="P4" t="n">
         <v>38400</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46650</v>
+        <v>46500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.33%</t>
+          <t>'+14.96%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>736</v>
+        <v>754</v>
       </c>
       <c r="F5" t="n">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G5" t="n">
-        <v>4506</v>
+        <v>4575</v>
       </c>
       <c r="H5" t="n">
         <v>14.1</v>
@@ -886,7 +886,7 @@
         <v>14.11</v>
       </c>
       <c r="O5" t="n">
-        <v>242850992100</v>
+        <v>245080996350</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5020</v>
+        <v>4970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.09%</t>
+          <t>'+12.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
         <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H6" t="n">
         <v>1.4</v>
@@ -978,7 +978,7 @@
         <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>134612271202</v>
+        <v>136207921422</v>
       </c>
       <c r="P6" t="n">
         <v>8100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3110</v>
+        <v>3165</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.31%</t>
+          <t>'+11.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>46773883341</v>
+        <v>48749955988</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1457</v>
+        <v>20400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.73%</t>
+          <t>'+8.57%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K8" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L8" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M8" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>19825018027</v>
+        <v>137592448565</v>
       </c>
       <c r="P8" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q8" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>-186000</v>
+        <v>-73000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>금융권 AI 공격 관련 보안주 동반 상승 전망. 양자 보안 기술 기반 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '양자보안', 'AI']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20400</v>
+        <v>1447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.57%</t>
+          <t>'+7.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18790</v>
+        <v>1340</v>
       </c>
       <c r="K9" t="n">
-        <v>21400</v>
+        <v>1370</v>
       </c>
       <c r="L9" t="n">
-        <v>22300</v>
+        <v>1555</v>
       </c>
       <c r="M9" t="n">
-        <v>20050</v>
+        <v>1360</v>
       </c>
       <c r="N9" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>136376862140</v>
+        <v>19934585602</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>2970</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>890</v>
       </c>
       <c r="R9" t="n">
-        <v>-73000</v>
+        <v>-186000</v>
       </c>
       <c r="S9" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>은행권 보안 위협에 따른 보안주 상승 기대감. 엑스게이트의 성장 가능성 언급.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '금융권']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18410</v>
+        <v>18360</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.43%</t>
+          <t>'+3.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="H10" t="n">
         <v>3.81</v>
@@ -1346,7 +1346,7 @@
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>207185894730</v>
+        <v>208873525515</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 함께 대한광통신이 대장주로 부상할 것이라는 긍정적 전망 제시.</t>
+          <t>미국 증시 광통신 섹터 강세 및 3분기 영업이익 개선. 전고점 돌파 및 매물 소화 과정 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '대장주', '매물 소화']</t>
+          <t>['광통신', '영업이익', '매물대']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1412,7 +1412,7 @@
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="H11" t="n">
         <v>9.390000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>54168460980</v>
+        <v>56454193950</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15400</v>
+        <v>15230</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'-0.78%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H12" t="n">
         <v>0.32</v>
@@ -1530,7 +1530,7 @@
         <v>0.18</v>
       </c>
       <c r="O12" t="n">
-        <v>67828512010</v>
+        <v>68423368400</v>
       </c>
       <c r="P12" t="n">
         <v>29750</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19630</v>
+        <v>19610</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
         <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H13" t="n">
         <v>27.78</v>
@@ -1622,7 +1622,7 @@
         <v>27.73</v>
       </c>
       <c r="O13" t="n">
-        <v>35334298345</v>
+        <v>36322357900</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>270250</v>
+        <v>270750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="G14" t="n">
-        <v>1515</v>
+        <v>1504</v>
       </c>
       <c r="H14" t="n">
         <v>46.41</v>
@@ -1714,7 +1714,7 @@
         <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>2257738350250</v>
+        <v>2355918488750</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>부정적인 의견 다수, 자사주 매입 중단 및 주가 하락에 대한 불만 표출.</t>
+          <t>분기 영업이익 100조 앞두고도 주가 부진. 정치적 요인 언급 및 자사주 매입 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '자사주', '주가']</t>
+          <t>['영업이익', '주가', '자사주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1777000</v>
+        <v>1774000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.64%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G15" t="n">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="H15" t="n">
         <v>49.76</v>
@@ -1800,13 +1800,13 @@
         <v>1837000</v>
       </c>
       <c r="M15" t="n">
-        <v>1776000</v>
+        <v>1771000</v>
       </c>
       <c r="N15" t="n">
         <v>49.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3059718780000</v>
+        <v>3177609838500</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 리스크 및 오너 리스크로 인한 주가 하락에 대한 강한 불만 표출. 주가 조작 의혹 제기.</t>
+          <t>오너 리스크 및 정치적 요인으로 인한 주가 부진. 외국인 매도세 및 ADR 상장 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['오너리스크', '정치', '주가조작']</t>
+          <t>['오너리스크', '외국인', 'ADR']</t>
         </is>
       </c>
       <c r="X15" t="n">
